--- a/docs/Mapping_casi_uso/matrimoni/Matr_999_2.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_999_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="210">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Data Evento</t>
@@ -694,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.65625" customWidth="true" bestFit="true"/>
@@ -990,13 +996,13 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -1010,16 +1016,16 @@
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -1033,13 +1039,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -1062,7 +1068,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -1085,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -1099,19 +1105,19 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -1122,16 +1128,16 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>52</v>
@@ -1145,16 +1151,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>54</v>
@@ -1168,16 +1174,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>56</v>
@@ -1191,7 +1197,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>57</v>
@@ -1200,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
@@ -1214,7 +1220,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>59</v>
@@ -1223,7 +1229,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -1237,7 +1243,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
@@ -1246,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1260,16 +1266,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1283,7 +1289,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -1292,7 +1298,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1306,7 +1312,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -1315,7 +1321,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1329,7 +1335,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
@@ -1338,7 +1344,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1352,7 +1358,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1361,7 +1367,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1375,16 +1381,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1398,7 +1404,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1407,7 +1413,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1421,16 +1427,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1444,7 +1450,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1453,7 +1459,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1467,7 +1473,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
@@ -1476,7 +1482,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1490,7 +1496,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
@@ -1499,7 +1505,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1513,7 +1519,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
@@ -1522,7 +1528,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1536,7 +1542,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
@@ -1545,7 +1551,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1559,7 +1565,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
@@ -1568,7 +1574,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1582,7 +1588,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
@@ -1591,7 +1597,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1605,7 +1611,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -1614,7 +1620,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1628,16 +1634,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1651,7 +1657,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
@@ -1660,7 +1666,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1674,16 +1680,16 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1697,7 +1703,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -1706,7 +1712,7 @@
         <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1720,7 +1726,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
@@ -1729,7 +1735,7 @@
         <v>25</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1743,7 +1749,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
@@ -1752,7 +1758,7 @@
         <v>25</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1766,7 +1772,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
@@ -1775,7 +1781,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1789,19 +1795,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -1812,16 +1818,16 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>52</v>
@@ -1835,16 +1841,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>54</v>
@@ -1858,16 +1864,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>56</v>
@@ -1881,7 +1887,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>57</v>
@@ -1890,7 +1896,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>58</v>
@@ -1904,7 +1910,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>59</v>
@@ -1913,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>60</v>
@@ -1927,7 +1933,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>61</v>
@@ -1936,7 +1942,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>62</v>
@@ -1950,16 +1956,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>64</v>
@@ -1973,7 +1979,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>65</v>
@@ -1982,7 +1988,7 @@
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>66</v>
@@ -1996,7 +2002,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>67</v>
@@ -2005,7 +2011,7 @@
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>68</v>
@@ -2019,7 +2025,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>69</v>
@@ -2028,7 +2034,7 @@
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>70</v>
@@ -2042,7 +2048,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>71</v>
@@ -2051,7 +2057,7 @@
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>72</v>
@@ -2065,16 +2071,16 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>74</v>
@@ -2088,7 +2094,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>75</v>
@@ -2097,7 +2103,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>76</v>
@@ -2111,16 +2117,16 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>78</v>
@@ -2134,7 +2140,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>79</v>
@@ -2143,7 +2149,7 @@
         <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>80</v>
@@ -2157,7 +2163,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>81</v>
@@ -2166,7 +2172,7 @@
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>82</v>
@@ -2180,7 +2186,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>83</v>
@@ -2189,7 +2195,7 @@
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>84</v>
@@ -2203,7 +2209,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>85</v>
@@ -2212,7 +2218,7 @@
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>86</v>
@@ -2226,7 +2232,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>87</v>
@@ -2235,7 +2241,7 @@
         <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>88</v>
@@ -2249,7 +2255,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>89</v>
@@ -2258,7 +2264,7 @@
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>90</v>
@@ -2272,7 +2278,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>91</v>
@@ -2281,7 +2287,7 @@
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>92</v>
@@ -2295,7 +2301,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>93</v>
@@ -2304,7 +2310,7 @@
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>94</v>
@@ -2318,16 +2324,16 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>96</v>
@@ -2341,7 +2347,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>97</v>
@@ -2350,7 +2356,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>98</v>
@@ -2364,16 +2370,16 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>100</v>
@@ -2387,7 +2393,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>101</v>
@@ -2396,7 +2402,7 @@
         <v>25</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>102</v>
@@ -2410,7 +2416,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>103</v>
@@ -2419,7 +2425,7 @@
         <v>25</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>104</v>
@@ -2433,7 +2439,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>105</v>
@@ -2442,7 +2448,7 @@
         <v>25</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>106</v>
@@ -2456,7 +2462,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>107</v>
@@ -2465,7 +2471,7 @@
         <v>25</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>108</v>
@@ -2482,7 +2488,7 @@
         <v>111</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
@@ -2491,27 +2497,27 @@
         <v>112</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>52</v>
@@ -2520,21 +2526,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>54</v>
@@ -2543,21 +2549,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>56</v>
@@ -2566,12 +2572,12 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>57</v>
@@ -2580,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>58</v>
@@ -2589,12 +2595,12 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>59</v>
@@ -2603,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>60</v>
@@ -2612,12 +2618,12 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>61</v>
@@ -2626,7 +2632,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>62</v>
@@ -2635,21 +2641,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>64</v>
@@ -2658,12 +2664,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>65</v>
@@ -2672,7 +2678,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>66</v>
@@ -2681,12 +2687,12 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>67</v>
@@ -2695,7 +2701,7 @@
         <v>25</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>68</v>
@@ -2704,12 +2710,12 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>69</v>
@@ -2718,7 +2724,7 @@
         <v>25</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>70</v>
@@ -2727,12 +2733,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>71</v>
@@ -2741,7 +2747,7 @@
         <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>72</v>
@@ -2750,12 +2756,12 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>73</v>
@@ -2764,7 +2770,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>74</v>
@@ -2773,12 +2779,12 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>75</v>
@@ -2787,7 +2793,7 @@
         <v>25</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>76</v>
@@ -2796,12 +2802,12 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>77</v>
@@ -2810,7 +2816,7 @@
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>78</v>
@@ -2819,12 +2825,12 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>79</v>
@@ -2833,7 +2839,7 @@
         <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>80</v>
@@ -2842,12 +2848,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>81</v>
@@ -2856,7 +2862,7 @@
         <v>25</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>82</v>
@@ -2865,12 +2871,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>83</v>
@@ -2879,7 +2885,7 @@
         <v>25</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>84</v>
@@ -2888,12 +2894,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>85</v>
@@ -2902,7 +2908,7 @@
         <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>86</v>
@@ -2911,12 +2917,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>87</v>
@@ -2925,7 +2931,7 @@
         <v>25</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>88</v>
@@ -2934,12 +2940,12 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>89</v>
@@ -2948,7 +2954,7 @@
         <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>90</v>
@@ -2957,12 +2963,12 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>91</v>
@@ -2971,7 +2977,7 @@
         <v>25</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>92</v>
@@ -2980,12 +2986,12 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>93</v>
@@ -2994,7 +3000,7 @@
         <v>25</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>94</v>
@@ -3003,21 +3009,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>96</v>
@@ -3026,12 +3032,12 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>97</v>
@@ -3040,7 +3046,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>98</v>
@@ -3049,21 +3055,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>100</v>
@@ -3072,44 +3078,44 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="E104" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>52</v>
@@ -3118,21 +3124,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>54</v>
@@ -3141,21 +3147,21 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>56</v>
@@ -3164,12 +3170,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>57</v>
@@ -3178,7 +3184,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>58</v>
@@ -3187,12 +3193,12 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>59</v>
@@ -3201,7 +3207,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>60</v>
@@ -3210,12 +3216,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>61</v>
@@ -3224,7 +3230,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>62</v>
@@ -3233,21 +3239,21 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>64</v>
@@ -3256,12 +3262,12 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>65</v>
@@ -3270,7 +3276,7 @@
         <v>25</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>66</v>
@@ -3279,12 +3285,12 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>67</v>
@@ -3293,7 +3299,7 @@
         <v>25</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>68</v>
@@ -3302,12 +3308,12 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>69</v>
@@ -3316,7 +3322,7 @@
         <v>25</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>70</v>
@@ -3325,12 +3331,12 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>71</v>
@@ -3339,7 +3345,7 @@
         <v>25</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>72</v>
@@ -3348,12 +3354,12 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>73</v>
@@ -3362,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>74</v>
@@ -3371,12 +3377,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>75</v>
@@ -3385,7 +3391,7 @@
         <v>25</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>76</v>
@@ -3394,12 +3400,12 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>77</v>
@@ -3408,7 +3414,7 @@
         <v>25</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>78</v>
@@ -3417,12 +3423,12 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>79</v>
@@ -3431,7 +3437,7 @@
         <v>25</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>80</v>
@@ -3440,12 +3446,12 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>81</v>
@@ -3454,7 +3460,7 @@
         <v>25</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>82</v>
@@ -3463,12 +3469,12 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>83</v>
@@ -3477,7 +3483,7 @@
         <v>25</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>84</v>
@@ -3486,12 +3492,12 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>85</v>
@@ -3500,7 +3506,7 @@
         <v>25</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>86</v>
@@ -3509,12 +3515,12 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>87</v>
@@ -3523,7 +3529,7 @@
         <v>25</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>88</v>
@@ -3532,12 +3538,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>89</v>
@@ -3546,7 +3552,7 @@
         <v>25</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>90</v>
@@ -3555,12 +3561,12 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>91</v>
@@ -3569,7 +3575,7 @@
         <v>25</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>92</v>
@@ -3578,12 +3584,12 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>93</v>
@@ -3592,7 +3598,7 @@
         <v>25</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>94</v>
@@ -3601,21 +3607,21 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>96</v>
@@ -3624,12 +3630,12 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>97</v>
@@ -3638,7 +3644,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>98</v>
@@ -3647,21 +3653,21 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>100</v>
@@ -3670,44 +3676,44 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D130" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D130" s="2" t="s">
+      <c r="E130" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>52</v>
@@ -3716,21 +3722,21 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>54</v>
@@ -3739,21 +3745,21 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>56</v>
@@ -3762,12 +3768,12 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>57</v>
@@ -3776,7 +3782,7 @@
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>58</v>
@@ -3785,12 +3791,12 @@
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>59</v>
@@ -3799,7 +3805,7 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>60</v>
@@ -3808,12 +3814,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>61</v>
@@ -3822,7 +3828,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>62</v>
@@ -3831,21 +3837,21 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>64</v>
@@ -3854,12 +3860,12 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>65</v>
@@ -3868,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>66</v>
@@ -3877,12 +3883,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>67</v>
@@ -3891,7 +3897,7 @@
         <v>25</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>68</v>
@@ -3900,12 +3906,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>69</v>
@@ -3914,7 +3920,7 @@
         <v>25</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>70</v>
@@ -3923,12 +3929,12 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>71</v>
@@ -3937,7 +3943,7 @@
         <v>25</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>72</v>
@@ -3946,12 +3952,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>73</v>
@@ -3960,7 +3966,7 @@
         <v>25</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>74</v>
@@ -3969,12 +3975,12 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>75</v>
@@ -3983,7 +3989,7 @@
         <v>25</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>76</v>
@@ -3992,12 +3998,12 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>77</v>
@@ -4006,7 +4012,7 @@
         <v>25</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>78</v>
@@ -4015,12 +4021,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>79</v>
@@ -4029,7 +4035,7 @@
         <v>25</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>80</v>
@@ -4038,12 +4044,12 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>81</v>
@@ -4052,7 +4058,7 @@
         <v>25</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>82</v>
@@ -4061,12 +4067,12 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>83</v>
@@ -4075,7 +4081,7 @@
         <v>25</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>84</v>
@@ -4084,12 +4090,12 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>85</v>
@@ -4098,7 +4104,7 @@
         <v>25</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>86</v>
@@ -4107,12 +4113,12 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>87</v>
@@ -4121,7 +4127,7 @@
         <v>25</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>88</v>
@@ -4130,12 +4136,12 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>89</v>
@@ -4144,7 +4150,7 @@
         <v>25</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>90</v>
@@ -4153,12 +4159,12 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>91</v>
@@ -4167,7 +4173,7 @@
         <v>25</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>92</v>
@@ -4176,12 +4182,12 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>93</v>
@@ -4190,7 +4196,7 @@
         <v>25</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>94</v>
@@ -4199,21 +4205,21 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>96</v>
@@ -4222,12 +4228,12 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>97</v>
@@ -4236,7 +4242,7 @@
         <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>98</v>
@@ -4245,21 +4251,21 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>100</v>
@@ -4268,44 +4274,44 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D156" s="2" t="s">
+      <c r="E156" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>52</v>
@@ -4314,21 +4320,21 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>54</v>
@@ -4337,21 +4343,21 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>56</v>
@@ -4360,12 +4366,12 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>57</v>
@@ -4374,7 +4380,7 @@
         <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>58</v>
@@ -4383,12 +4389,12 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>59</v>
@@ -4397,7 +4403,7 @@
         <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>60</v>
@@ -4406,12 +4412,12 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>61</v>
@@ -4420,7 +4426,7 @@
         <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>62</v>
@@ -4429,21 +4435,21 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>64</v>
@@ -4452,12 +4458,12 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>65</v>
@@ -4466,7 +4472,7 @@
         <v>25</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>66</v>
@@ -4475,12 +4481,12 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>67</v>
@@ -4489,7 +4495,7 @@
         <v>25</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>68</v>
@@ -4498,12 +4504,12 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>69</v>
@@ -4512,7 +4518,7 @@
         <v>25</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>70</v>
@@ -4521,12 +4527,12 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>71</v>
@@ -4535,7 +4541,7 @@
         <v>25</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>72</v>
@@ -4544,12 +4550,12 @@
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>73</v>
@@ -4558,7 +4564,7 @@
         <v>25</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>74</v>
@@ -4567,12 +4573,12 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>75</v>
@@ -4581,7 +4587,7 @@
         <v>25</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>76</v>
@@ -4590,12 +4596,12 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>77</v>
@@ -4604,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>78</v>
@@ -4613,12 +4619,12 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>79</v>
@@ -4627,7 +4633,7 @@
         <v>25</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>80</v>
@@ -4636,12 +4642,12 @@
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>81</v>
@@ -4650,7 +4656,7 @@
         <v>25</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>82</v>
@@ -4659,12 +4665,12 @@
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>83</v>
@@ -4673,7 +4679,7 @@
         <v>25</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>84</v>
@@ -4682,12 +4688,12 @@
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>85</v>
@@ -4696,7 +4702,7 @@
         <v>25</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>86</v>
@@ -4705,12 +4711,12 @@
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>87</v>
@@ -4719,7 +4725,7 @@
         <v>25</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>88</v>
@@ -4728,12 +4734,12 @@
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>89</v>
@@ -4742,7 +4748,7 @@
         <v>25</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>90</v>
@@ -4751,12 +4757,12 @@
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>91</v>
@@ -4765,7 +4771,7 @@
         <v>25</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>92</v>
@@ -4774,12 +4780,12 @@
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>93</v>
@@ -4788,7 +4794,7 @@
         <v>25</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>94</v>
@@ -4797,21 +4803,21 @@
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>96</v>
@@ -4820,12 +4826,12 @@
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>97</v>
@@ -4834,7 +4840,7 @@
         <v>9</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>98</v>
@@ -4843,21 +4849,21 @@
         <v>10</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>100</v>
@@ -4866,67 +4872,67 @@
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D182" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="E182" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C183" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D183" s="2" t="s">
+      <c r="F183" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D184" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>131</v>
@@ -4935,58 +4941,58 @@
         <v>10</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G185" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F186" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>43</v>
@@ -4995,21 +5001,21 @@
         <v>25</v>
       </c>
       <c r="D187" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G187" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>45</v>
@@ -5018,30 +5024,30 @@
         <v>25</v>
       </c>
       <c r="D188" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G188" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>135</v>
@@ -5050,12 +5056,12 @@
         <v>10</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>136</v>
@@ -5064,7 +5070,7 @@
         <v>25</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>137</v>
@@ -5073,12 +5079,12 @@
         <v>10</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>138</v>
@@ -5087,7 +5093,7 @@
         <v>25</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>139</v>
@@ -5096,12 +5102,12 @@
         <v>10</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>140</v>
@@ -5110,7 +5116,7 @@
         <v>25</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>141</v>
@@ -5119,44 +5125,44 @@
         <v>10</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B193" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E193" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="F193" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>131</v>
@@ -5165,58 +5171,58 @@
         <v>10</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C195" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="E195" s="2" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>43</v>
@@ -5225,21 +5231,21 @@
         <v>25</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>45</v>
@@ -5248,30 +5254,30 @@
         <v>25</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>135</v>
@@ -5280,12 +5286,12 @@
         <v>10</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>136</v>
@@ -5294,7 +5300,7 @@
         <v>25</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>137</v>
@@ -5303,12 +5309,12 @@
         <v>10</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>138</v>
@@ -5317,7 +5323,7 @@
         <v>25</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>139</v>
@@ -5326,12 +5332,12 @@
         <v>10</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>140</v>
@@ -5340,7 +5346,7 @@
         <v>25</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>141</v>
@@ -5349,44 +5355,44 @@
         <v>10</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G203" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D204" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>151</v>
@@ -5400,7 +5406,7 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>152</v>
@@ -5409,7 +5415,7 @@
         <v>25</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>153</v>
@@ -5423,7 +5429,7 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>154</v>
@@ -5432,7 +5438,7 @@
         <v>25</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>155</v>
@@ -5446,7 +5452,7 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>156</v>
@@ -5455,7 +5461,7 @@
         <v>25</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>157</v>
@@ -5469,7 +5475,7 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>158</v>
@@ -5478,7 +5484,7 @@
         <v>25</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>159</v>
@@ -5492,7 +5498,7 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>160</v>
@@ -5501,10 +5507,10 @@
         <v>25</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>10</v>
@@ -5515,19 +5521,19 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>10</v>
@@ -5538,7 +5544,7 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>163</v>
@@ -5547,10 +5553,10 @@
         <v>25</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>10</v>
@@ -5561,19 +5567,19 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>10</v>
@@ -5584,7 +5590,7 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>166</v>
@@ -5593,7 +5599,7 @@
         <v>25</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>167</v>
@@ -5607,7 +5613,7 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>168</v>
@@ -5616,7 +5622,7 @@
         <v>25</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>169</v>
@@ -5630,7 +5636,7 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>170</v>
@@ -5639,7 +5645,7 @@
         <v>25</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>171</v>
@@ -5653,19 +5659,19 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="C216" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D216" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>10</v>
@@ -5676,16 +5682,16 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>151</v>
@@ -5699,7 +5705,7 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>152</v>
@@ -5708,7 +5714,7 @@
         <v>25</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>153</v>
@@ -5722,7 +5728,7 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>154</v>
@@ -5731,7 +5737,7 @@
         <v>25</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>155</v>
@@ -5745,7 +5751,7 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>156</v>
@@ -5754,7 +5760,7 @@
         <v>25</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>157</v>
@@ -5768,7 +5774,7 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>158</v>
@@ -5777,7 +5783,7 @@
         <v>25</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>159</v>
@@ -5791,7 +5797,7 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>160</v>
@@ -5800,10 +5806,10 @@
         <v>25</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>10</v>
@@ -5814,19 +5820,19 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>10</v>
@@ -5837,7 +5843,7 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>163</v>
@@ -5846,10 +5852,10 @@
         <v>25</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>10</v>
@@ -5860,19 +5866,19 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>10</v>
@@ -5883,7 +5889,7 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>166</v>
@@ -5892,7 +5898,7 @@
         <v>25</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>167</v>
@@ -5906,7 +5912,7 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>168</v>
@@ -5915,7 +5921,7 @@
         <v>25</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>169</v>
@@ -5929,7 +5935,7 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>170</v>
@@ -5938,7 +5944,7 @@
         <v>25</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>171</v>
@@ -5955,50 +5961,50 @@
         <v>174</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C229" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="E229" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>178</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C230" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E230" s="2" t="s">
+      <c r="F230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>181</v>
@@ -6007,7 +6013,7 @@
         <v>25</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>182</v>
@@ -6016,12 +6022,12 @@
         <v>10</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>183</v>
@@ -6030,7 +6036,7 @@
         <v>25</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>184</v>
@@ -6039,12 +6045,12 @@
         <v>10</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>185</v>
@@ -6053,7 +6059,7 @@
         <v>25</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>186</v>
@@ -6062,12 +6068,12 @@
         <v>10</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>187</v>
@@ -6076,7 +6082,7 @@
         <v>25</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>188</v>
@@ -6085,12 +6091,12 @@
         <v>10</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>189</v>
@@ -6099,7 +6105,7 @@
         <v>25</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>190</v>
@@ -6108,21 +6114,21 @@
         <v>10</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>14</v>
+        <v>178</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>192</v>
@@ -6131,7 +6137,7 @@
         <v>10</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
     </row>
     <row r="237">
@@ -6139,16 +6145,16 @@
         <v>193</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>10</v>
@@ -6159,7 +6165,7 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>196</v>
@@ -6168,7 +6174,7 @@
         <v>9</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>197</v>
@@ -6182,7 +6188,7 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>198</v>
@@ -6191,7 +6197,7 @@
         <v>9</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>199</v>
@@ -6205,19 +6211,19 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="C240" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>10</v>
@@ -6228,16 +6234,16 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B241" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D241" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>205</v>
@@ -6251,7 +6257,7 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>206</v>
@@ -6260,7 +6266,7 @@
         <v>25</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>207</v>
@@ -6274,24 +6280,47 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B243" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B244" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C243" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E243" s="2" t="s">
+      <c r="C244" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E244" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F243" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G243" s="2" t="s">
+      <c r="F244" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G244" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_999_2.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_999_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="216">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -712,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H257"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.65625" customWidth="true" bestFit="true"/>
@@ -771,63 +777,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -836,90 +842,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -928,21 +934,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -951,12 +957,12 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -965,7 +971,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -974,21 +980,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -997,21 +1003,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -1020,12 +1026,12 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>37</v>
@@ -1034,53 +1040,53 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -1089,21 +1095,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -1112,21 +1118,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -1135,44 +1141,44 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>54</v>
@@ -1181,21 +1187,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>56</v>
@@ -1204,12 +1210,12 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>57</v>
@@ -1218,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
@@ -1227,21 +1233,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -1250,21 +1256,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1273,12 +1279,12 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -1287,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1296,21 +1302,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1319,21 +1325,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1342,21 +1348,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1365,21 +1371,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1388,21 +1394,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1411,21 +1417,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1434,21 +1440,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1457,12 +1463,12 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1471,7 +1477,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1480,21 +1486,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1503,21 +1509,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1526,21 +1532,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1549,21 +1555,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1572,21 +1578,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1595,21 +1601,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1618,21 +1624,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1641,21 +1647,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1664,21 +1670,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1687,21 +1693,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1710,12 +1716,12 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -1724,7 +1730,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1733,21 +1739,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1756,21 +1762,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1779,21 +1785,21 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1802,21 +1808,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
@@ -1825,21 +1831,21 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>112</v>
@@ -1848,21 +1854,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1871,44 +1877,44 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>54</v>
@@ -1917,21 +1923,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>56</v>
@@ -1940,12 +1946,12 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>57</v>
@@ -1954,7 +1960,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>58</v>
@@ -1963,21 +1969,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>60</v>
@@ -1986,21 +1992,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>62</v>
@@ -2009,12 +2015,12 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>63</v>
@@ -2023,7 +2029,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>64</v>
@@ -2032,21 +2038,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>66</v>
@@ -2055,21 +2061,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>68</v>
@@ -2078,21 +2084,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>70</v>
@@ -2101,21 +2107,21 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>72</v>
@@ -2124,21 +2130,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>74</v>
@@ -2147,21 +2153,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>76</v>
@@ -2170,21 +2176,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>78</v>
@@ -2193,12 +2199,12 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>79</v>
@@ -2207,7 +2213,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>80</v>
@@ -2216,21 +2222,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>82</v>
@@ -2239,21 +2245,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>84</v>
@@ -2262,21 +2268,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>86</v>
@@ -2285,21 +2291,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>88</v>
@@ -2308,21 +2314,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>90</v>
@@ -2331,21 +2337,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>92</v>
@@ -2354,21 +2360,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>94</v>
@@ -2377,21 +2383,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>96</v>
@@ -2400,21 +2406,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>98</v>
@@ -2423,21 +2429,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>100</v>
@@ -2446,12 +2452,12 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>101</v>
@@ -2460,7 +2466,7 @@
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>102</v>
@@ -2469,21 +2475,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>104</v>
@@ -2492,21 +2498,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>106</v>
@@ -2515,21 +2521,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>108</v>
@@ -2538,21 +2544,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>110</v>
@@ -2561,21 +2567,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>112</v>
@@ -2584,21 +2590,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>114</v>
@@ -2607,7 +2613,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -2615,36 +2621,36 @@
         <v>117</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>54</v>
@@ -2653,21 +2659,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>56</v>
@@ -2676,12 +2682,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>57</v>
@@ -2690,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>58</v>
@@ -2699,21 +2705,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>60</v>
@@ -2722,21 +2728,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>62</v>
@@ -2745,12 +2751,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>63</v>
@@ -2759,7 +2765,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>64</v>
@@ -2768,21 +2774,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>66</v>
@@ -2791,21 +2797,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>68</v>
@@ -2814,21 +2820,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>70</v>
@@ -2837,21 +2843,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>72</v>
@@ -2860,21 +2866,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>74</v>
@@ -2883,21 +2889,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>76</v>
@@ -2906,21 +2912,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>78</v>
@@ -2929,21 +2935,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>80</v>
@@ -2952,21 +2958,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>82</v>
@@ -2975,21 +2981,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>84</v>
@@ -2998,21 +3004,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>86</v>
@@ -3021,21 +3027,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>88</v>
@@ -3044,21 +3050,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>90</v>
@@ -3067,21 +3073,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>92</v>
@@ -3090,21 +3096,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>94</v>
@@ -3113,21 +3119,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>96</v>
@@ -3136,21 +3142,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>98</v>
@@ -3159,21 +3165,21 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>100</v>
@@ -3182,12 +3188,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>101</v>
@@ -3196,7 +3202,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>102</v>
@@ -3205,21 +3211,21 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>104</v>
@@ -3228,21 +3234,21 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>106</v>
@@ -3251,44 +3257,44 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D111" s="2" t="s">
+      <c r="E111" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>54</v>
@@ -3297,21 +3303,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>56</v>
@@ -3320,12 +3326,12 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>57</v>
@@ -3334,7 +3340,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>58</v>
@@ -3343,21 +3349,21 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>60</v>
@@ -3366,21 +3372,21 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>62</v>
@@ -3389,12 +3395,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>63</v>
@@ -3403,7 +3409,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>64</v>
@@ -3412,21 +3418,21 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>66</v>
@@ -3435,21 +3441,21 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>68</v>
@@ -3458,21 +3464,21 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>70</v>
@@ -3481,21 +3487,21 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>72</v>
@@ -3504,21 +3510,21 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>74</v>
@@ -3527,21 +3533,21 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>76</v>
@@ -3550,21 +3556,21 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>78</v>
@@ -3573,21 +3579,21 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>80</v>
@@ -3596,21 +3602,21 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>82</v>
@@ -3619,21 +3625,21 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>84</v>
@@ -3642,21 +3648,21 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>86</v>
@@ -3665,21 +3671,21 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>88</v>
@@ -3688,21 +3694,21 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>90</v>
@@ -3711,21 +3717,21 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>92</v>
@@ -3734,21 +3740,21 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>94</v>
@@ -3757,21 +3763,21 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>96</v>
@@ -3780,21 +3786,21 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>98</v>
@@ -3803,21 +3809,21 @@
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>100</v>
@@ -3826,12 +3832,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>101</v>
@@ -3840,7 +3846,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>102</v>
@@ -3849,21 +3855,21 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>104</v>
@@ -3872,21 +3878,21 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>106</v>
@@ -3895,44 +3901,44 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D139" s="2" t="s">
+      <c r="E139" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>54</v>
@@ -3941,21 +3947,21 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>56</v>
@@ -3964,12 +3970,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>57</v>
@@ -3978,7 +3984,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>58</v>
@@ -3987,21 +3993,21 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>60</v>
@@ -4010,21 +4016,21 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>62</v>
@@ -4033,12 +4039,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>63</v>
@@ -4047,7 +4053,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>64</v>
@@ -4056,21 +4062,21 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>66</v>
@@ -4079,21 +4085,21 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>68</v>
@@ -4102,21 +4108,21 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>70</v>
@@ -4125,21 +4131,21 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>72</v>
@@ -4148,21 +4154,21 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>74</v>
@@ -4171,21 +4177,21 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>76</v>
@@ -4194,21 +4200,21 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>78</v>
@@ -4217,21 +4223,21 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>80</v>
@@ -4240,21 +4246,21 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>82</v>
@@ -4263,21 +4269,21 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>84</v>
@@ -4286,21 +4292,21 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>86</v>
@@ -4309,21 +4315,21 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>88</v>
@@ -4332,21 +4338,21 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>90</v>
@@ -4355,21 +4361,21 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>92</v>
@@ -4378,21 +4384,21 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>94</v>
@@ -4401,21 +4407,21 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>96</v>
@@ -4424,21 +4430,21 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>98</v>
@@ -4447,21 +4453,21 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>100</v>
@@ -4470,12 +4476,12 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>101</v>
@@ -4484,7 +4490,7 @@
         <v>9</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>102</v>
@@ -4493,21 +4499,21 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>104</v>
@@ -4516,21 +4522,21 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>106</v>
@@ -4539,44 +4545,44 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D167" s="2" t="s">
+      <c r="E167" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>54</v>
@@ -4585,21 +4591,21 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>56</v>
@@ -4608,12 +4614,12 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>57</v>
@@ -4622,7 +4628,7 @@
         <v>9</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>58</v>
@@ -4631,21 +4637,21 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>60</v>
@@ -4654,21 +4660,21 @@
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>62</v>
@@ -4677,12 +4683,12 @@
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>63</v>
@@ -4691,7 +4697,7 @@
         <v>9</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>64</v>
@@ -4700,21 +4706,21 @@
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>66</v>
@@ -4723,21 +4729,21 @@
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>68</v>
@@ -4746,21 +4752,21 @@
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>70</v>
@@ -4769,21 +4775,21 @@
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>72</v>
@@ -4792,21 +4798,21 @@
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>74</v>
@@ -4815,21 +4821,21 @@
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>76</v>
@@ -4838,21 +4844,21 @@
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>78</v>
@@ -4861,21 +4867,21 @@
         <v>10</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>80</v>
@@ -4884,21 +4890,21 @@
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>82</v>
@@ -4907,21 +4913,21 @@
         <v>10</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>84</v>
@@ -4930,21 +4936,21 @@
         <v>10</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>86</v>
@@ -4953,21 +4959,21 @@
         <v>10</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>88</v>
@@ -4976,21 +4982,21 @@
         <v>10</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>90</v>
@@ -4999,21 +5005,21 @@
         <v>10</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>92</v>
@@ -5022,21 +5028,21 @@
         <v>10</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>94</v>
@@ -5045,21 +5051,21 @@
         <v>10</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>96</v>
@@ -5068,21 +5074,21 @@
         <v>10</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>98</v>
@@ -5091,21 +5097,21 @@
         <v>10</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>100</v>
@@ -5114,12 +5120,12 @@
         <v>10</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>101</v>
@@ -5128,7 +5134,7 @@
         <v>9</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>102</v>
@@ -5137,21 +5143,21 @@
         <v>10</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>104</v>
@@ -5160,21 +5166,21 @@
         <v>10</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>106</v>
@@ -5183,67 +5189,67 @@
         <v>10</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="E195" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D196" s="2" t="s">
+      <c r="F196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>137</v>
@@ -5252,113 +5258,113 @@
         <v>10</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D198" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G198" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D199" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D200" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D201" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G201" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>141</v>
@@ -5367,21 +5373,21 @@
         <v>10</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>143</v>
@@ -5390,21 +5396,21 @@
         <v>10</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>145</v>
@@ -5413,21 +5419,21 @@
         <v>10</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>147</v>
@@ -5436,44 +5442,44 @@
         <v>10</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="C206" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E206" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="F206" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>137</v>
@@ -5482,113 +5488,113 @@
         <v>10</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D208" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C208" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="E208" s="2" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>141</v>
@@ -5597,21 +5603,21 @@
         <v>10</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>143</v>
@@ -5620,21 +5626,21 @@
         <v>10</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>145</v>
@@ -5643,21 +5649,21 @@
         <v>10</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>147</v>
@@ -5666,44 +5672,44 @@
         <v>10</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G216" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D217" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>157</v>
@@ -5712,21 +5718,21 @@
         <v>10</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>159</v>
@@ -5735,21 +5741,21 @@
         <v>10</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>161</v>
@@ -5758,21 +5764,21 @@
         <v>10</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>163</v>
@@ -5781,21 +5787,21 @@
         <v>10</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>165</v>
@@ -5804,113 +5810,113 @@
         <v>10</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>173</v>
@@ -5919,21 +5925,21 @@
         <v>10</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>175</v>
@@ -5942,21 +5948,21 @@
         <v>10</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>177</v>
@@ -5965,44 +5971,44 @@
         <v>10</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="C229" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D229" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E229" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F229" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>157</v>
@@ -6011,21 +6017,21 @@
         <v>10</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>159</v>
@@ -6034,21 +6040,21 @@
         <v>10</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>161</v>
@@ -6057,21 +6063,21 @@
         <v>10</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>163</v>
@@ -6080,21 +6086,21 @@
         <v>10</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>165</v>
@@ -6103,113 +6109,113 @@
         <v>10</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>173</v>
@@ -6218,21 +6224,21 @@
         <v>10</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>175</v>
@@ -6241,21 +6247,21 @@
         <v>10</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>177</v>
@@ -6264,7 +6270,7 @@
         <v>10</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="242">
@@ -6272,59 +6278,59 @@
         <v>180</v>
       </c>
       <c r="B242" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D242" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C242" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="E242" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>184</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B243" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C243" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E243" s="2" t="s">
+      <c r="F243" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G243" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>188</v>
@@ -6333,21 +6339,21 @@
         <v>10</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>190</v>
@@ -6356,21 +6362,21 @@
         <v>10</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>192</v>
@@ -6379,21 +6385,21 @@
         <v>10</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>194</v>
@@ -6402,21 +6408,21 @@
         <v>10</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>196</v>
@@ -6425,12 +6431,12 @@
         <v>10</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>197</v>
@@ -6439,7 +6445,7 @@
         <v>9</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>198</v>
@@ -6448,7 +6454,7 @@
         <v>10</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
     </row>
     <row r="250">
@@ -6456,36 +6462,36 @@
         <v>199</v>
       </c>
       <c r="B250" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E250" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C250" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="F250" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>203</v>
@@ -6494,21 +6500,21 @@
         <v>10</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>205</v>
@@ -6517,44 +6523,44 @@
         <v>10</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="C253" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C253" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F253" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>211</v>
@@ -6563,21 +6569,21 @@
         <v>10</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>212</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>213</v>
@@ -6586,30 +6592,53 @@
         <v>10</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D256" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E256" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G256" s="2" t="s">
-        <v>16</v>
+      <c r="B257" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
